--- a/public/Examination/2026年季度GMV目标模板_202610231201.xlsx
+++ b/public/Examination/2026年季度GMV目标模板_202610231201.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Peidi\peidi-pm-frontend\public\Examination\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95DE8F90-BBEC-4A90-851F-3289FA6194C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01931507-F8F2-4E17-A3BA-0363259CF469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="255">
   <si>
     <t>2026年度第四季度GMV目标确认</t>
   </si>
@@ -789,6 +789,10 @@
   </si>
   <si>
     <t>及时达</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>个人销售收入（GSV)</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -1106,17 +1110,8 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1130,11 +1125,20 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1491,7 +1495,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="35" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="17" t="s">
@@ -1515,7 +1519,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
+      <c r="A4" s="35"/>
       <c r="B4" s="20" t="s">
         <v>16</v>
       </c>
@@ -1537,7 +1541,7 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
+      <c r="A5" s="35"/>
       <c r="B5" s="20" t="s">
         <v>20</v>
       </c>
@@ -1559,7 +1563,7 @@
       </c>
     </row>
     <row r="6" spans="1:10" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
+      <c r="A6" s="35"/>
       <c r="B6" s="20" t="s">
         <v>22</v>
       </c>
@@ -1582,7 +1586,7 @@
       <c r="J6" s="6"/>
     </row>
     <row r="7" spans="1:10" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
+      <c r="A7" s="35"/>
       <c r="B7" s="20" t="s">
         <v>25</v>
       </c>
@@ -1605,7 +1609,7 @@
       <c r="J7" s="6"/>
     </row>
     <row r="8" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
+      <c r="A8" s="35"/>
       <c r="B8" s="20" t="s">
         <v>27</v>
       </c>
@@ -1627,12 +1631,12 @@
       </c>
     </row>
     <row r="9" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="32" t="s">
+      <c r="A9" s="35"/>
+      <c r="B9" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
       <c r="E9" s="23">
         <f>SUBTOTAL(9,E4:E8)</f>
         <v>0</v>
@@ -1679,7 +1683,7 @@
       <c r="J10" s="6"/>
     </row>
     <row r="11" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="35" t="s">
         <v>30</v>
       </c>
       <c r="B11" s="24" t="s">
@@ -1703,7 +1707,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
+      <c r="A12" s="35"/>
       <c r="B12" s="20" t="s">
         <v>33</v>
       </c>
@@ -1725,12 +1729,12 @@
       </c>
     </row>
     <row r="13" spans="1:10" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="32" t="s">
+      <c r="A13" s="35"/>
+      <c r="B13" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="23">
         <f>SUBTOTAL(9,E12:E12)</f>
         <v>0</v>
@@ -1779,7 +1783,7 @@
       <c r="J14" s="6"/>
     </row>
     <row r="15" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="35" t="s">
         <v>35</v>
       </c>
       <c r="B15" s="24" t="s">
@@ -1803,7 +1807,7 @@
       </c>
     </row>
     <row r="16" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="33"/>
+      <c r="A16" s="35"/>
       <c r="B16" s="20" t="s">
         <v>38</v>
       </c>
@@ -1825,7 +1829,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="33"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="20" t="s">
         <v>42</v>
       </c>
@@ -1847,7 +1851,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
+      <c r="A18" s="35"/>
       <c r="B18" s="20" t="s">
         <v>44</v>
       </c>
@@ -1869,12 +1873,12 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="33"/>
-      <c r="B19" s="32" t="s">
+      <c r="A19" s="35"/>
+      <c r="B19" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
       <c r="E19" s="23">
         <f>SUBTOTAL(9,E16:E18)</f>
         <v>0</v>
@@ -1923,7 +1927,7 @@
       <c r="J20" s="6"/>
     </row>
     <row r="21" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="35" t="s">
         <v>46</v>
       </c>
       <c r="B21" s="24" t="s">
@@ -1947,7 +1951,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="33"/>
+      <c r="A22" s="35"/>
       <c r="B22" s="20" t="s">
         <v>49</v>
       </c>
@@ -1969,12 +1973,12 @@
       </c>
     </row>
     <row r="23" spans="1:10" s="8" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
-      <c r="B23" s="32" t="s">
+      <c r="A23" s="35"/>
+      <c r="B23" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
       <c r="E23" s="23">
         <f>SUBTOTAL(9,E22:E22)</f>
         <v>0</v>
@@ -2023,7 +2027,7 @@
       <c r="J24" s="6"/>
     </row>
     <row r="25" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="35" t="s">
         <v>53</v>
       </c>
       <c r="B25" s="25" t="s">
@@ -2047,7 +2051,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="33"/>
+      <c r="A26" s="35"/>
       <c r="B26" s="20" t="s">
         <v>57</v>
       </c>
@@ -2069,7 +2073,7 @@
       </c>
     </row>
     <row r="27" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="33"/>
+      <c r="A27" s="35"/>
       <c r="B27" s="20" t="s">
         <v>60</v>
       </c>
@@ -2091,7 +2095,7 @@
       </c>
     </row>
     <row r="28" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
+      <c r="A28" s="35"/>
       <c r="B28" s="20" t="s">
         <v>60</v>
       </c>
@@ -2113,7 +2117,7 @@
       </c>
     </row>
     <row r="29" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="33"/>
+      <c r="A29" s="35"/>
       <c r="B29" s="20" t="s">
         <v>63</v>
       </c>
@@ -2135,7 +2139,7 @@
       </c>
     </row>
     <row r="30" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="33"/>
+      <c r="A30" s="35"/>
       <c r="B30" s="20" t="s">
         <v>65</v>
       </c>
@@ -2157,7 +2161,7 @@
       </c>
     </row>
     <row r="31" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="33"/>
+      <c r="A31" s="35"/>
       <c r="B31" s="20" t="s">
         <v>65</v>
       </c>
@@ -2179,7 +2183,7 @@
       </c>
     </row>
     <row r="32" spans="1:10" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="33"/>
+      <c r="A32" s="35"/>
       <c r="B32" s="20" t="s">
         <v>65</v>
       </c>
@@ -2201,7 +2205,7 @@
       </c>
     </row>
     <row r="33" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="33"/>
+      <c r="A33" s="35"/>
       <c r="B33" s="20" t="s">
         <v>69</v>
       </c>
@@ -2223,7 +2227,7 @@
       </c>
     </row>
     <row r="34" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="33"/>
+      <c r="A34" s="35"/>
       <c r="B34" s="20" t="s">
         <v>71</v>
       </c>
@@ -2240,12 +2244,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I34" s="6" t="s">
-        <v>56</v>
+      <c r="I34" s="29" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="35" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="33"/>
+      <c r="A35" s="35"/>
       <c r="B35" s="20" t="s">
         <v>71</v>
       </c>
@@ -2262,12 +2266,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I35" s="6" t="s">
-        <v>56</v>
+      <c r="I35" s="29" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="33"/>
+      <c r="A36" s="35"/>
       <c r="B36" s="20" t="s">
         <v>71</v>
       </c>
@@ -2284,12 +2288,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I36" s="6" t="s">
-        <v>56</v>
+      <c r="I36" s="29" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="37" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="33"/>
+      <c r="A37" s="35"/>
       <c r="B37" s="20" t="s">
         <v>71</v>
       </c>
@@ -2306,12 +2310,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I37" s="6" t="s">
-        <v>56</v>
+      <c r="I37" s="29" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="38" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
+      <c r="A38" s="35"/>
       <c r="B38" s="20" t="s">
         <v>71</v>
       </c>
@@ -2328,17 +2332,17 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I38" s="6" t="s">
-        <v>56</v>
+      <c r="I38" s="29" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="39" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="33"/>
-      <c r="B39" s="32" t="s">
+      <c r="A39" s="35"/>
+      <c r="B39" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
       <c r="E39" s="23">
         <f>SUBTOTAL(9,E26:E38)</f>
         <v>0</v>
@@ -2388,7 +2392,7 @@
       <c r="M40" s="6"/>
     </row>
     <row r="41" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="34" t="s">
+      <c r="A41" s="31" t="s">
         <v>77</v>
       </c>
       <c r="B41" s="25" t="s">
@@ -2415,7 +2419,7 @@
       <c r="M41" s="5"/>
     </row>
     <row r="42" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="35"/>
+      <c r="A42" s="32"/>
       <c r="B42" s="20" t="s">
         <v>80</v>
       </c>
@@ -2437,7 +2441,7 @@
       </c>
     </row>
     <row r="43" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="36"/>
+      <c r="A43" s="33"/>
       <c r="B43" s="20" t="s">
         <v>80</v>
       </c>
@@ -2459,12 +2463,12 @@
       </c>
     </row>
     <row r="44" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="37"/>
-      <c r="B44" s="32" t="s">
+      <c r="A44" s="34"/>
+      <c r="B44" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
       <c r="E44" s="23">
         <f>SUBTOTAL(9,E42:E43)</f>
         <v>0</v>
@@ -2514,7 +2518,7 @@
       <c r="M45" s="6"/>
     </row>
     <row r="46" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="33" t="s">
+      <c r="A46" s="35" t="s">
         <v>84</v>
       </c>
       <c r="B46" s="25" t="s">
@@ -2541,11 +2545,11 @@
       <c r="M46" s="5"/>
     </row>
     <row r="47" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="33"/>
-      <c r="B47" s="38" t="s">
+      <c r="A47" s="35"/>
+      <c r="B47" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="C47" s="30" t="s">
+      <c r="C47" s="38" t="s">
         <v>89</v>
       </c>
       <c r="D47" s="21" t="s">
@@ -2563,9 +2567,9 @@
       </c>
     </row>
     <row r="48" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="33"/>
-      <c r="B48" s="39"/>
-      <c r="C48" s="31"/>
+      <c r="A48" s="35"/>
+      <c r="B48" s="37"/>
+      <c r="C48" s="39"/>
       <c r="D48" s="21" t="s">
         <v>92</v>
       </c>
@@ -2581,11 +2585,11 @@
       </c>
     </row>
     <row r="49" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="33"/>
-      <c r="B49" s="38" t="s">
+      <c r="A49" s="35"/>
+      <c r="B49" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="C49" s="30" t="s">
+      <c r="C49" s="38" t="s">
         <v>93</v>
       </c>
       <c r="D49" s="21" t="s">
@@ -2603,9 +2607,9 @@
       </c>
     </row>
     <row r="50" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="33"/>
-      <c r="B50" s="39"/>
-      <c r="C50" s="31"/>
+      <c r="A50" s="35"/>
+      <c r="B50" s="37"/>
+      <c r="C50" s="39"/>
       <c r="D50" s="21" t="s">
         <v>92</v>
       </c>
@@ -2621,7 +2625,7 @@
       </c>
     </row>
     <row r="51" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="33"/>
+      <c r="A51" s="35"/>
       <c r="B51" s="20" t="s">
         <v>94</v>
       </c>
@@ -2643,12 +2647,12 @@
       </c>
     </row>
     <row r="52" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="33"/>
-      <c r="B52" s="32" t="s">
+      <c r="A52" s="35"/>
+      <c r="B52" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
       <c r="E52" s="23">
         <f>SUBTOTAL(9,E47:E51)</f>
         <v>0</v>
@@ -2698,7 +2702,7 @@
       <c r="M53" s="6"/>
     </row>
     <row r="54" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="33" t="s">
+      <c r="A54" s="35" t="s">
         <v>97</v>
       </c>
       <c r="B54" s="25" t="s">
@@ -2723,7 +2727,7 @@
       <c r="M54" s="5"/>
     </row>
     <row r="55" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="33"/>
+      <c r="A55" s="35"/>
       <c r="B55" s="20" t="s">
         <v>100</v>
       </c>
@@ -2747,7 +2751,7 @@
       <c r="L55" s="5"/>
     </row>
     <row r="56" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="33"/>
+      <c r="A56" s="35"/>
       <c r="B56" s="20" t="s">
         <v>100</v>
       </c>
@@ -2769,12 +2773,12 @@
       </c>
     </row>
     <row r="57" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="33"/>
-      <c r="B57" s="32" t="s">
+      <c r="A57" s="35"/>
+      <c r="B57" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
       <c r="E57" s="23">
         <f>SUBTOTAL(9,E55:E56)</f>
         <v>0</v>
@@ -2824,7 +2828,7 @@
       <c r="M58" s="6"/>
     </row>
     <row r="59" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="33" t="s">
+      <c r="A59" s="35" t="s">
         <v>103</v>
       </c>
       <c r="B59" s="25" t="s">
@@ -2849,7 +2853,7 @@
       <c r="M59" s="5"/>
     </row>
     <row r="60" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="33"/>
+      <c r="A60" s="35"/>
       <c r="B60" s="20" t="s">
         <v>88</v>
       </c>
@@ -2873,12 +2877,12 @@
       <c r="L60" s="5"/>
     </row>
     <row r="61" spans="1:13" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="33"/>
-      <c r="B61" s="32" t="s">
+      <c r="A61" s="35"/>
+      <c r="B61" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C61" s="32"/>
-      <c r="D61" s="32"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
       <c r="E61" s="23">
         <f>SUBTOTAL(9,E60)</f>
         <v>0</v>
@@ -2971,28 +2975,28 @@
   </sheetData>
   <autoFilter ref="A2:J67" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="22">
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A25:A39"/>
     <mergeCell ref="A41:A44"/>
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A54:A57"/>
     <mergeCell ref="A59:A61"/>
     <mergeCell ref="B47:B48"/>
     <mergeCell ref="B49:B50"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A25:A39"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B39:D39"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.29861111111111099" footer="0.29861111111111099"/>
